--- a/data/trans_dic/P21B_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21B_R2-Estudios-trans_dic.xlsx
@@ -664,29 +664,29 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2,28%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2,66%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,81</t>
+          <t>1,74; 8,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,56</t>
+          <t>0,4; 4,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 3,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,44</t>
+          <t>0,6; 5,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,85</t>
+          <t>0,82; 3,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,24</t>
+          <t>0,25; 2,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,44</t>
+          <t>0,0; 3,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,49</t>
+          <t>1,14; 4,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,5</t>
+          <t>1,62; 4,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,57</t>
+          <t>0,61; 2,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,54</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,85</t>
+          <t>1,24; 4,02</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,1</t>
+          <t>0,97; 5,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,19</t>
+          <t>0,8; 4,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,52</t>
+          <t>4,31; 10,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,61</t>
+          <t>3,57; 9,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,09</t>
+          <t>1,39; 4,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,76</t>
+          <t>1,49; 4,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,68</t>
+          <t>3,57; 8,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,78</t>
+          <t>5,56; 10,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,17</t>
+          <t>1,66; 4,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,88</t>
+          <t>1,52; 3,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,66; 8,59</t>
+          <t>4,66; 8,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 7,52</t>
+          <t>5,28; 9,08</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 21,38</t>
+          <t>4,4; 20,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 13,19</t>
+          <t>1,57; 14,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,5; 24,97</t>
+          <t>7,68; 25,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,96; 28,58</t>
+          <t>13,01; 26,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 12,88</t>
+          <t>2,6; 13,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,26; 19,08</t>
+          <t>6,57; 19,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,98; 29,94</t>
+          <t>14,33; 29,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,85; 20,48</t>
+          <t>11,35; 21,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 13,28</t>
+          <t>3,96; 13,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 14,78</t>
+          <t>5,89; 15,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,08; 24,8</t>
+          <t>13,5; 24,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,58; 22,22</t>
+          <t>12,96; 21,22</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,27</t>
+          <t>2,59; 6,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,76</t>
+          <t>1,4; 3,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 9,21</t>
+          <t>4,37; 8,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 10,73</t>
+          <t>5,9; 10,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,31</t>
+          <t>1,93; 4,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,34</t>
+          <t>2,14; 4,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 9,54</t>
+          <t>5,38; 9,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,55</t>
+          <t>6,32; 9,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,5</t>
+          <t>2,49; 4,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,74</t>
+          <t>2,03; 3,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,52</t>
+          <t>5,56; 8,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,53</t>
+          <t>6,54; 9,36</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>8548</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3682; 15443</t>
+          <t>3447; 15985</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1010; 11399</t>
+          <t>1001; 10130</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5545</t>
+          <t>0; 5150</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>811; 7197</t>
+          <t>849; 7333</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2955; 13152</t>
+          <t>2807; 12899</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1808; 13269</t>
+          <t>1043; 11508</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 9905</t>
+          <t>0; 7962</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2125; 9831</t>
+          <t>2722; 11497</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8491; 24253</t>
+          <t>8723; 24753</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4000; 16939</t>
+          <t>4007; 17600</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>987; 9162</t>
+          <t>0; 9397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4099; 13537</t>
+          <t>4725; 15292</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22476</t>
+          <t>24774</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35836</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58311</t>
+          <t>63728</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2681; 14338</t>
+          <t>2712; 14776</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3056; 16086</t>
+          <t>3077; 16311</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14768; 35409</t>
+          <t>14500; 36039</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14157; 38794</t>
+          <t>15389; 40981</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5477; 19145</t>
+          <t>5218; 18503</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6636; 21491</t>
+          <t>6727; 21622</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13981; 33648</t>
+          <t>13818; 33809</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13064; 57475</t>
+          <t>27954; 51203</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10710; 27392</t>
+          <t>10930; 28678</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12415; 32374</t>
+          <t>12682; 32509</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33772; 62195</t>
+          <t>33759; 61355</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26969; 79582</t>
+          <t>49297; 84846</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28177</t>
+          <t>29966</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26109</t>
+          <t>29245</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54286</t>
+          <t>59210</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3837; 17020</t>
+          <t>3500; 16196</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>965; 9161</t>
+          <t>1087; 9876</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5543; 18448</t>
+          <t>5672; 18483</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19468; 39842</t>
+          <t>20728; 42562</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2355; 13661</t>
+          <t>2756; 13834</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7154; 21804</t>
+          <t>7506; 22035</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18759; 40195</t>
+          <t>19228; 39136</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18577; 35050</t>
+          <t>21579; 40058</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8206; 24653</t>
+          <t>7345; 24296</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10183; 27161</t>
+          <t>10827; 28489</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27212; 51607</t>
+          <t>28100; 50863</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42164; 69001</t>
+          <t>45279; 74161</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53665</t>
+          <t>57833</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>66627</t>
+          <t>73654</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>120292</t>
+          <t>131486</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15263; 35006</t>
+          <t>14448; 35954</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9074; 26428</t>
+          <t>9839; 26868</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24718; 50448</t>
+          <t>23948; 48853</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40352; 72485</t>
+          <t>43185; 77943</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15672; 35543</t>
+          <t>15880; 35103</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19325; 42352</t>
+          <t>20901; 43734</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41033; 71102</t>
+          <t>40101; 71208</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34834; 89376</t>
+          <t>58943; 91308</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33647; 62143</t>
+          <t>34462; 62244</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33811; 62766</t>
+          <t>34053; 64896</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71835; 110120</t>
+          <t>71924; 108536</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>78575; 146687</t>
+          <t>108810; 155850</t>
         </is>
       </c>
     </row>
